--- a/artfynd/A 64290-2021 artfynd.xlsx
+++ b/artfynd/A 64290-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
@@ -1516,6 +1516,125 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103486695</v>
+      </c>
+      <c r="B9" t="n">
+        <v>89776</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ej möjlig att validera</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stigen, Granön, Kalix skg., Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>891171</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7316332</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Stoltz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Stoltz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64290-2021 artfynd.xlsx
+++ b/artfynd/A 64290-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100078708</v>
+        <v>102254508</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Strandviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Primula nutans</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Georgi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granön, Nb</t>
+          <t>Strandäng Granöns S/V sida 3-4 km, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>890583.6912366628</v>
+        <v>890858</v>
       </c>
       <c r="R2" t="n">
-        <v>7317018.934246709</v>
+        <v>7316486</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,37 +762,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maria Stoltz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maria Stoltz</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100078711</v>
+        <v>100078708</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,11 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>890593.392813243</v>
+        <v>890584</v>
       </c>
       <c r="R3" t="n">
-        <v>7317021.094331403</v>
+        <v>7317019</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,19 +853,9 @@
           <t>2022-04-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,19 +882,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100078712</v>
+        <v>100078711</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -947,7 +913,11 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>890695.2277643045</v>
+        <v>890593</v>
       </c>
       <c r="R4" t="n">
-        <v>7316980.112119982</v>
+        <v>7317021</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,19 +958,9 @@
           <t>2022-04-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102202418</v>
+        <v>100078712</v>
       </c>
       <c r="B5" t="n">
-        <v>96245</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,45 +998,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223572</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strandäng Granöns S/V sida 3-4 km, Nb</t>
+          <t>Granön, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>890857.5208202032</v>
+        <v>890694</v>
       </c>
       <c r="R5" t="n">
-        <v>7316485.50547842</v>
+        <v>7316980</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,22 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,34 +1070,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Stoltz</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Stoltz</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102254508</v>
+        <v>110311461</v>
       </c>
       <c r="B6" t="n">
-        <v>103167</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,45 +1099,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1295</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Strandviva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula nutans</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Georgi</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strandäng Granöns S/V sida 3-4 km, Nb</t>
+          <t>Granön, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>890857.5208202032</v>
+        <v>891053</v>
       </c>
       <c r="R6" t="n">
-        <v>7316485.50547842</v>
+        <v>7316466</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,22 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1175,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1269,37 +1193,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103486695</v>
+        <v>103486000</v>
       </c>
       <c r="B7" t="n">
-        <v>89863</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ej möjlig att validera</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>256756</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1307,23 +1226,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stigen, Granön, Kalix skg., Nb</t>
+          <t>Göl, Granön, Kalix skg., Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>891170</v>
+        <v>891216</v>
       </c>
       <c r="R7" t="n">
-        <v>7316333</v>
+        <v>7316310</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,12 +1278,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-06-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2022-06-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,56 +1292,50 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Myr</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Stoltz</t>
+          <t>Unni Stoltz</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Stoltz</t>
+          <t>Unni Stoltz</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110311461</v>
+        <v>101211104</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>208260</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1421,28 +1343,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granön, Nb</t>
+          <t>Granön Blombäck, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>891053.5501158009</v>
+        <v>890486</v>
       </c>
       <c r="R8" t="n">
-        <v>7316465.745468291</v>
+        <v>7316915</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,22 +1393,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,21 +1407,128 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Unni Stoltz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Unni Stoltz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102202418</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99028</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Strandäng Granöns S/V sida 3-4 km, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>890858</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7316486</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-07-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Maria Stoltz</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Maria Stoltz</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
